--- a/public/raw-entry-data/b2c/Arch & Analysis.xlsx
+++ b/public/raw-entry-data/b2c/Arch & Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alfa/web-alfa/tr-b2c/tech-radar/public/raw-entry-data/b2c/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FA34B7-ACB0-1845-B9AE-46D423F55E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E867FB-94BA-2446-AC3F-53471B63272F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="1640" windowWidth="31840" windowHeight="12300" xr2:uid="{D0E5AF86-51E4-4329-BFCB-5FE4200F8556}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="120">
   <si>
     <t>Ноль</t>
   </si>
@@ -96,9 +96,6 @@
     <t>ai</t>
   </si>
   <si>
-    <t>pluntuml</t>
-  </si>
-  <si>
     <t>Knowledge level</t>
   </si>
   <si>
@@ -127,12 +124,6 @@
   </si>
   <si>
     <t>https://www.npmjs.com/package/rest</t>
-  </si>
-  <si>
-    <t>https://www.npmjs.com/package/pluntuml</t>
-  </si>
-  <si>
-    <t>plantuml (likely pluntuml) renders UML diagrams from plain‑text descriptions.</t>
   </si>
   <si>
     <t>comment</t>
@@ -214,19 +205,10 @@
     <t>Redis</t>
   </si>
   <si>
-    <t>mongoDB</t>
-  </si>
-  <si>
     <t>Apache Kafka</t>
   </si>
   <si>
     <t>auth</t>
-  </si>
-  <si>
-    <t>MongoDB — это популярная NoSQL СУБД, или система управления базами данных, которая предназначена для хранения больших объемов данных в формате документов.</t>
-  </si>
-  <si>
-    <t>https://www.mongodb.com/?version=latest</t>
   </si>
   <si>
     <t>https://redis.io/</t>
@@ -382,6 +364,45 @@
   </si>
   <si>
     <t>Подход к разработке интерфейсов, в котором сервер определяет не только данные, но и структуру, логику и контент интерфейса</t>
+  </si>
+  <si>
+    <t>git</t>
+  </si>
+  <si>
+    <t>GitLab</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/</t>
+  </si>
+  <si>
+    <t>GitLab — платформа для управления проектами и репозиториями, которая работает с системой версий Git.</t>
+  </si>
+  <si>
+    <t>Event Streaming</t>
+  </si>
+  <si>
+    <t>Event stream processing (ESP) — термин, который означает «обработка потоков событий». Так называют технологию, которая позволяет анализировать и действовать на непрерывные потоки данных (потоки событий) в реальном времени или почти в реальном времени.</t>
+  </si>
+  <si>
+    <t>https://maddevs.io/glossary/event-streaming/</t>
+  </si>
+  <si>
+    <t>Zitadel</t>
+  </si>
+  <si>
+    <t>https://zitadel.com/</t>
+  </si>
+  <si>
+    <t>это платформа управления идентификацией и доступом с открытым исходным кодом. Она обеспечивает безопасный вход, управление пользователями и контроль доступа.</t>
+  </si>
+  <si>
+    <t>https://plantuml.com/ru/</t>
+  </si>
+  <si>
+    <t>plantuml  renders UML diagrams from plain‑text descriptions.</t>
+  </si>
+  <si>
+    <t>plantuml</t>
   </si>
 </sst>
 </file>
@@ -511,8 +532,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D373D6EA-0DEB-453C-A593-8D3D82EAAFD4}" name="Таблица1" displayName="Таблица1" ref="A1:I1048408" totalsRowShown="0" headerRowCellStyle="Акцент1">
-  <autoFilter ref="A1:I1048408" xr:uid="{D373D6EA-0DEB-453C-A593-8D3D82EAAFD4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D373D6EA-0DEB-453C-A593-8D3D82EAAFD4}" name="Таблица1" displayName="Таблица1" ref="A1:I1048407" totalsRowShown="0" headerRowCellStyle="Акцент1">
+  <autoFilter ref="A1:I1048407" xr:uid="{D373D6EA-0DEB-453C-A593-8D3D82EAAFD4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I6">
     <sortCondition ref="A2:A6"/>
     <sortCondition ref="B2:B6"/>
@@ -849,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E083F0B-9B6B-4AE1-B88F-228D13850335}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
@@ -865,31 +886,31 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -900,16 +921,16 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -920,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
@@ -929,7 +950,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -937,10 +958,10 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
         <v>4</v>
@@ -949,7 +970,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>30</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -960,16 +981,16 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -977,19 +998,19 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -997,10 +1018,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>4</v>
@@ -1009,107 +1030,107 @@
         <v>6</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1117,19 +1138,19 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>70</v>
+        <v>66</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -1137,156 +1158,156 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
         <v>73</v>
       </c>
-      <c r="E14" t="s">
-        <v>79</v>
-      </c>
       <c r="F14" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" t="s">
         <v>76</v>
       </c>
-      <c r="E15" t="s">
-        <v>79</v>
-      </c>
       <c r="F15" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="B17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="E18" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="B19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>106</v>
@@ -1294,22 +1315,62 @@
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="2" t="s">
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
         <v>111</v>
       </c>
-      <c r="E22" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="D23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1319,22 +1380,24 @@
     <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
     <hyperlink ref="D4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
     <hyperlink ref="D8" r:id="rId5" xr:uid="{06EB6029-C718-824C-93B6-AD4B8D932173}"/>
-    <hyperlink ref="D10" r:id="rId6" xr:uid="{F0078C95-8F44-954D-AAA3-5091A0DFC043}"/>
-    <hyperlink ref="D9" r:id="rId7" xr:uid="{8396D4A7-F089-494F-9098-02E7DFB95112}"/>
-    <hyperlink ref="D12" r:id="rId8" xr:uid="{D749A71B-E58E-4D4B-A977-51E1E9873834}"/>
-    <hyperlink ref="D14" r:id="rId9" location="B2CShoppingApp.Архитектураипаттерны-Слоисервисов" xr:uid="{1F2315E8-2215-CD4F-90EE-854FFA963B2B}"/>
-    <hyperlink ref="D15" r:id="rId10" location="B2CShoppingApp.Архитектураипаттерны-Пограничныйслой(Gateway)" xr:uid="{16EF2841-C7F0-4746-A772-335B1AB4EA1C}"/>
-    <hyperlink ref="D2" r:id="rId11" xr:uid="{50FB1743-62C1-7E44-9FAA-694A8FBFD6D1}"/>
-    <hyperlink ref="D18" r:id="rId12" xr:uid="{75D00D31-8613-6B49-8DC0-2875105EBD92}"/>
-    <hyperlink ref="D19" r:id="rId13" xr:uid="{D335AC01-1172-654E-950C-C97A38D01203}"/>
-    <hyperlink ref="D20" r:id="rId14" xr:uid="{8AB1D43B-7F97-194F-8E3F-7B833109F301}"/>
-    <hyperlink ref="D21" r:id="rId15" xr:uid="{6183BC22-471C-554B-8FB2-2D8658840C13}"/>
-    <hyperlink ref="D22" r:id="rId16" xr:uid="{EBF07F6D-A8D3-6F47-8D17-6FA971738D75}"/>
+    <hyperlink ref="D9" r:id="rId6" xr:uid="{8396D4A7-F089-494F-9098-02E7DFB95112}"/>
+    <hyperlink ref="D11" r:id="rId7" xr:uid="{D749A71B-E58E-4D4B-A977-51E1E9873834}"/>
+    <hyperlink ref="D13" r:id="rId8" location="B2CShoppingApp.Архитектураипаттерны-Слоисервисов" xr:uid="{1F2315E8-2215-CD4F-90EE-854FFA963B2B}"/>
+    <hyperlink ref="D14" r:id="rId9" location="B2CShoppingApp.Архитектураипаттерны-Пограничныйслой(Gateway)" xr:uid="{16EF2841-C7F0-4746-A772-335B1AB4EA1C}"/>
+    <hyperlink ref="D2" r:id="rId10" xr:uid="{50FB1743-62C1-7E44-9FAA-694A8FBFD6D1}"/>
+    <hyperlink ref="D17" r:id="rId11" xr:uid="{75D00D31-8613-6B49-8DC0-2875105EBD92}"/>
+    <hyperlink ref="D18" r:id="rId12" xr:uid="{D335AC01-1172-654E-950C-C97A38D01203}"/>
+    <hyperlink ref="D19" r:id="rId13" xr:uid="{8AB1D43B-7F97-194F-8E3F-7B833109F301}"/>
+    <hyperlink ref="D20" r:id="rId14" xr:uid="{6183BC22-471C-554B-8FB2-2D8658840C13}"/>
+    <hyperlink ref="D21" r:id="rId15" xr:uid="{EBF07F6D-A8D3-6F47-8D17-6FA971738D75}"/>
+    <hyperlink ref="D22" r:id="rId16" xr:uid="{3DFDDA31-B13A-5345-9CE1-3DF9C227BBF3}"/>
+    <hyperlink ref="D23" r:id="rId17" xr:uid="{60C3CA7C-65DA-214A-B871-241BAB1F5727}"/>
+    <hyperlink ref="D24" r:id="rId18" xr:uid="{D9167226-25D9-8846-9EAD-7FD24C505D45}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId17"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId19"/>
   <tableParts count="1">
-    <tablePart r:id="rId18"/>
+    <tablePart r:id="rId20"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -1343,37 +1406,37 @@
           <x14:formula1>
             <xm:f>meta!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>F23:F97</xm:sqref>
+          <xm:sqref>F25:F96</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6857320C-10DD-4851-98FA-A3CA686293DC}">
           <x14:formula1>
             <xm:f>meta!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>E23:E94</xm:sqref>
+          <xm:sqref>E25:E93</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D7A50CBD-4525-4A5B-95B9-5C2666B34ED9}">
           <x14:formula1>
             <xm:f>rings!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>F16:F21</xm:sqref>
+          <xm:sqref>F15:F20</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5AFEE91B-7A0C-0045-8A32-2A47382063B4}">
           <x14:formula1>
             <xm:f>rings!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F15 F22</xm:sqref>
+          <xm:sqref>F21:F24 F2:F14</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6E5D21C0-46D9-574F-924F-47FF86B1D17A}">
           <x14:formula1>
             <xm:f>quadrants!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E22</xm:sqref>
+          <xm:sqref>E2:E24</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ECCB302B-B329-497F-B6B4-042AE8F9E14B}">
           <x14:formula1>
             <xm:f>meta!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I119</xm:sqref>
+          <xm:sqref>I2:I118</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1392,18 +1455,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1411,23 +1474,23 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1448,13 +1511,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1462,21 +1525,21 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1484,10 +1547,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1495,10 +1558,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1516,10 +1579,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1527,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1535,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
